--- a/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\PI2026\Intersecciones\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17976EB6-A0FF-4A63-AAD3-8E388397810B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326272EB-7305-4724-8B50-2D1BF396F78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8424" yWindow="4248" windowWidth="11976" windowHeight="7992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="1108">
   <si>
     <t>ubigeo_gestor</t>
   </si>
@@ -3344,6 +3344,9 @@
   </si>
   <si>
     <t>I-6270</t>
+  </si>
+  <si>
+    <t>I-6263</t>
   </si>
 </sst>
 </file>
@@ -11674,8 +11677,8 @@
       <c r="D276" t="s">
         <v>10</v>
       </c>
-      <c r="E276">
-        <v>6263</v>
+      <c r="E276" t="s">
+        <v>1107</v>
       </c>
       <c r="F276" t="s">
         <v>1075</v>

--- a/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-LIMA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I283"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-155686</t>
+          <t>I-99134</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.1158919</t>
+          <t>-12.0887043</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.8732456</t>
+          <t>-76.8699667</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Víctor Malásquez / Calle s / n</t>
+          <t>Los Constructores / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-156310</t>
+          <t>I-98356</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-11.9694561</t>
+          <t>-12.1512504</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.937414</t>
+          <t>-76.9792259</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Unión Jicamarca / Calle Bolognesi</t>
+          <t>Avenida Los Héroes / Calle Las Fresas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-172771</t>
+          <t>I-97671</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.2964243</t>
+          <t>-11.8972601</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.8509571</t>
+          <t>-77.030015</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Sur / Jirón 7 de Junio</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-337677</t>
+          <t>I-95315</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-11.9257052</t>
+          <t>-12.1670486</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9636162</t>
+          <t>-76.949869</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Pachacútec / Wiracocha</t>
+          <t>Avenida El Triunfo / Avenida Nicolás de Piérola</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-395798</t>
+          <t>I-93465</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.227659</t>
+          <t>-12.0419083</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.860808</t>
+          <t>-76.9654322</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jirón Comercio / Jirón Suspiros</t>
+          <t>Avenida Huancaray / Avenida Santa Rosa / Calle Chavín</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-152334</t>
+          <t>I-93330</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.0706369</t>
+          <t>-12.1950692</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.03157845</t>
+          <t>-77.0014774</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Isabel La Católica / Avenida Paseo de la República / Vía Expresa Luis Fernán Bedoya Reyes</t>
+          <t>Avenida Caminos del Inca / Jirón Leoncio Prado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-554052</t>
+          <t>I-92193</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.05132</t>
+          <t>-12.2526713</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-77.0364582</t>
+          <t>-76.897967</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jirón Camaná / Jirón Quilca</t>
+          <t>Antigua Panamericana Sur / Jirón Los Olivos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-16821</t>
+          <t>I-92028</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-11.9671086</t>
+          <t>-11.9734721</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.7419699</t>
+          <t>-76.7649977</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida California / Avenida Nicolás Ayllón</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,27 +909,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-175849</t>
+          <t>I-89490</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-11.9666848</t>
+          <t>-11.9372754</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.7415894</t>
+          <t>-77.0489711</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida California / Calle s / n</t>
+          <t>Avenida Túpac Amaru / Los Cactus</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-30298</t>
+          <t>I-89306</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-11.8654246</t>
+          <t>-11.930191</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-77.078941</t>
+          <t>-77.0534599</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida Ricardo Palma / Avenida Sucre</t>
+          <t>Avenida Micaela Bastidas / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-100271</t>
+          <t>I-88778</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.2201736</t>
+          <t>-11.927936</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.9304303</t>
+          <t>-77.0522899</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Calle B</t>
+          <t>Avenida Universitaria / Calle José Santos Atahuaipa</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-102917</t>
+          <t>I-8773</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.0144721</t>
+          <t>-12.0766035</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-76.8392907</t>
+          <t>-76.9961052</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Jaime Zubieta Calderon / Calle s / n</t>
+          <t>Avenida Del Aire / Jirón Rio Chira</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,27 +1097,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-104809</t>
+          <t>I-8770</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.167074</t>
+          <t>-12.075317</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-76.9518449</t>
+          <t>-76.9912288</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Pachacútec / Avenida Villa María</t>
+          <t>Auxiliar Avenida Circunvalación / Jirón Trinidad</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-105255</t>
+          <t>I-792383</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.0240107</t>
+          <t>-12.0853501</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-76.9774565</t>
+          <t>-76.8889466</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Malecon Miguel Checa Eguiguren / Jirón Los Paujiles</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-108893</t>
+          <t>I-783659</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.1876693</t>
+          <t>-12.0702149</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-76.9586899</t>
+          <t>-76.9944527</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Miguel Iglesias / Los Nardos</t>
+          <t>Auxiliar Avenida Circunvalación / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-109084</t>
+          <t>I-777501</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-11.8573551</t>
+          <t>-12.0670326</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-77.0680587</t>
+          <t>-76.9969118</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Avenida Lecaros / Calle s / n</t>
+          <t>Jirón Hector Marisca / Auxiliar Avenida Circunvalación</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-109806</t>
+          <t>I-77065</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-11.9751356</t>
+          <t>-11.9162314</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-76.7717618</t>
+          <t>-77.0411424</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Avenida Malecón Manco Cápac / Calle Los Robles</t>
+          <t>Avenida Túpac Amaru / Calle San Juan Bautista</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-109980</t>
+          <t>I-761437</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.0356324</t>
+          <t>-12.0687618</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-76.9488912</t>
+          <t>-77.0484618</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Avenida Huancaray / Avenida Metropolitana / Avenida de La Cultura</t>
+          <t>Avenida Brasil / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-113444</t>
+          <t>I-749340</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-11.9719159</t>
+          <t>-12.1675915</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-77.0755251</t>
+          <t>-76.9784144</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida Río Marañon / Avenida Universitaria</t>
+          <t>Avenida Alipio Ponce / Avenida Pedro Miotta</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-114053</t>
+          <t>I-748465</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-11.9539257</t>
+          <t>-12.091591</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-77.0516219</t>
+          <t>-77.008457</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Santa Cruz / Avenida Túpac Amaru</t>
+          <t>Avenida Guardia Civil / Calle 44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-114905</t>
+          <t>I-748018</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-11.970241</t>
+          <t>-12.0861374</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-77.0059095</t>
+          <t>-77.0355273</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida Canto Grande / Avenida Las Flores / Lloque Llupanqui</t>
+          <t>Avenida Julio César Tello / Avenida Álvarez de Arenales</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-115963</t>
+          <t>I-736851</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-11.9646572</t>
+          <t>-12.0056996</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-77.0552137</t>
+          <t>-76.8642115</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Jirón Miguel Grau</t>
+          <t>Avenida Ramiro Prialé / Calle Los Sauces</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-116632</t>
+          <t>I-687369</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-11.9934576</t>
+          <t>-12.0778822</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-77.0565083</t>
+          <t>-76.8566454</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cesar Vallejo / María Parado de Bellido</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-117769</t>
+          <t>I-6823</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-11.9615295</t>
+          <t>-12.1014778</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-76.9828702</t>
+          <t>-77.0667181</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Avenida Héroes del Cenepa Oeste / Los Geologos / Nicolas Heres</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,27 +1661,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-119925</t>
+          <t>I-681300</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-11.9332644</t>
+          <t>-12.1819848</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-76.9688159</t>
+          <t>-76.9423705</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avenida Fernando Wiesse / Avenida Pachacútec / Jirón Mar del Norte</t>
+          <t>Avenida Pachacútec / Calle Albino Torres</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1708,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-120450</t>
+          <t>I-6809</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.0062929</t>
+          <t>-12.0663389</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-77.0822386</t>
+          <t>-77.0542325</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Avenida Angélica Gamarra / Avenida Universitaria</t>
+          <t>Jirón Pedro Ruiz Gallo / Ovalo Breña</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1755,27 +1755,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-120958</t>
+          <t>I-6758</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-11.9958872</t>
+          <t>-12.0678335</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-77.0834199</t>
+          <t>-77.0605732</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Santiago Antúnez de Mayolo / Avenida Universitaria / Rio Santa</t>
+          <t>Avenida Paso de los Andes / Plaza de la Bandera</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1802,27 +1802,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-121247</t>
+          <t>I-6637</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-11.9917882</t>
+          <t>-12.0781154</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-77.0751161</t>
+          <t>-77.0107659</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Carlos Alberto Izaguirre / Conococha</t>
+          <t>Avenida Aviación / Óvalo de Arriola</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-121622</t>
+          <t>I-6270</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-11.9949537</t>
+          <t>-12.0472822</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-77.0769602</t>
+          <t>-77.0454346</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avenida Santiago Antúnez de Mayolo / Daniel Hernandez / Hernandaz</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-122328</t>
+          <t>I-6263</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-11.912586</t>
+          <t>-12.0477024</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-77.0036922</t>
+          <t>-77.0453965</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Avenida Revolución / Jirón Santa Rosa</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-122923</t>
+          <t>I-6253</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-12.0551807</t>
+          <t>-12.0627362</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-77.0040035</t>
+          <t>-77.0437682</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Avenida Mártir José Olaya / El Agustino / Santa Isabel</t>
+          <t>Avenida Brasil / Jirón Don Bosco</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-124607</t>
+          <t>I-6117</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-11.9230559</t>
+          <t>-12.162338</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-77.0767791</t>
+          <t>-77.0259681</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Calle 16 / Calle s / n</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-125829</t>
+          <t>I-588266</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-11.9636651</t>
+          <t>-12.1544387</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-77.0925209</t>
+          <t>-76.8692864</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Avenida Tantamayo / Calle 23</t>
+          <t>Avenida Víctor Malásquez / Calle Las Rosas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,27 +2084,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-127177</t>
+          <t>I-583974</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-12.0607028</t>
+          <t>-12.0846493</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-77.0588482</t>
+          <t>-76.8634587</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Avenida Tingo María / Jirón Chamaya</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2131,27 +2131,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-127791</t>
+          <t>I-574584</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-12.197277</t>
+          <t>-12.300693</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-76.9529804</t>
+          <t>-76.7893688</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Avenida Micaela Bastidas / Calle 2 / Calle 7</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2178,27 +2178,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-127869</t>
+          <t>I-574545</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-12.2187471</t>
+          <t>-12.3009928</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-76.9399948</t>
+          <t>-76.7916584</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Avenida Bolívar / Avenida Micaela Bastidas</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2225,27 +2225,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-132628</t>
+          <t>I-574452</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-12.0913633</t>
+          <t>-12.2904145</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-77.0673503</t>
+          <t>-76.7624038</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Jirón San Martín</t>
+          <t>Avenida Pampa Pacta / Calle s / n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2272,27 +2272,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-133645</t>
+          <t>I-574449</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-12.059654</t>
+          <t>-12.2984865</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-77.0298397</t>
+          <t>-76.7807326</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Avenida Manco Cápac / Calle s / n</t>
+          <t>Avenida Pampa Pacta / Calle s / n</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2319,27 +2319,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-135778</t>
+          <t>I-5687</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-12.07610484</t>
+          <t>-12.3001175</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-77.02762207</t>
+          <t>-76.8453082</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Avenida Manco Cápac / Avenida México / Avenida Paseo de la República</t>
+          <t>Antigua Panamericana Sur / Avenida Industrial</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-135791</t>
+          <t>I-554052</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-12.0358187</t>
+          <t>-12.05132</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-76.9996691</t>
+          <t>-77.0364582</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Avenida Ferrocarril / Los Zorzales</t>
+          <t>Jirón Camaná / Jirón Quilca</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-137012</t>
+          <t>I-553657</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-11.9755819</t>
+          <t>-12.0970493</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-76.772891</t>
+          <t>-77.0715608</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Avenida Malecón Manco Cápac / Calle Los Naranjos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2460,22 +2460,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I-137776</t>
+          <t>I-511125</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-12.2355103</t>
+          <t>-12.0263356</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-76.9162344</t>
+          <t>-76.8923119</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Avenida Separadora Industrial / Pasaje 9</t>
+          <t>Calle Los Halcones / Avenida Alfonso Ugarte</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2507,27 +2507,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I-137799</t>
+          <t>I-5065</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-12.1227253</t>
+          <t>-11.9525292</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-76.8155333</t>
+          <t>-77.0514694</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Avenida Nueva Toledo / Calle Pacayal</t>
+          <t>Avenida 22 de Agosto / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2554,22 +2554,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I-138062</t>
+          <t>I-4986</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-12.1616654</t>
+          <t>-11.9886777</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-76.9650321</t>
+          <t>-77.0808392</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Avenida Guillermo Billinghurst / Valentín Espejo</t>
+          <t>Avenida Los Olivos / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I-138197</t>
+          <t>I-4578</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-12.15943151</t>
+          <t>-12.1156861</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-76.95873889</t>
+          <t>-77.0102719</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Avenida Los Héroes / Avenida Miguel Iglesias</t>
+          <t>Alejandro Deustua / Avenida de Tomás Marsano / República del Salvador</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2648,27 +2648,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I-142706</t>
+          <t>I-4477</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-12.1898993</t>
+          <t>-12.13407441</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-77.0065322</t>
+          <t>-77.02055953</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Avenida Defensores del Morro / Calle Rinconada de Villa</t>
+          <t>Calle Metropolitano / Calle Vía Expresa Luis Fernán Bedoya Reyes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2695,27 +2695,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I-143121</t>
+          <t>I-442184</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-12.2245075</t>
+          <t>-12.2213482</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-76.938757</t>
+          <t>-76.9202054</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Calle E</t>
+          <t>Avenida 6 / Avenida Pachacútec</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2742,27 +2742,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I-145305</t>
+          <t>I-436514</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-12.1802321</t>
+          <t>-11.9742495</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-76.9979157</t>
+          <t>-76.7689808</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Avenida Guardia Civil Sur / Avenida de la Guardia Civil / Calle Los Meteoros</t>
+          <t>Avenida Malecón Manco Cápac / Calle s / n</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2789,22 +2789,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I-145496</t>
+          <t>I-431785</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-12.2448713</t>
+          <t>-12.0063421</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-76.9202892</t>
+          <t>-76.8302505</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Calle 20 / Calle s / n</t>
+          <t>Avenida Los Incas / Calle s / n</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>I-148244</t>
+          <t>I-431746</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-12.0819895</t>
+          <t>-12.1521436</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-76.928718</t>
+          <t>-77.0246022</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Avenida 7 / Calle s / n</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2883,27 +2883,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>I-151221</t>
+          <t>I-430050</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-12.0316811</t>
+          <t>-12.0903621</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-76.9501879</t>
+          <t>-76.8560453</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Avenida de La Cultura / Calle 11</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2930,27 +2930,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I-1519</t>
+          <t>I-421732</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-12.0319059</t>
+          <t>-12.2382054</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-77.075132</t>
+          <t>-76.8606208</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Avenida Perú / Calle s / n</t>
+          <t>Avenida Camino Real / Calle s / n</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2977,27 +2977,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>I-156039</t>
+          <t>I-4212</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-12.0292721</t>
+          <t>-12.0754842</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-77.0178999</t>
+          <t>-77.0439545</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Avenida Principal / Avenida Rímac</t>
+          <t>Jirón Huayna Cápac / Calle s / n</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3024,27 +3024,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>I-157768</t>
+          <t>I-4210</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-11.8213548</t>
+          <t>-12.0795977</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-77.103016</t>
+          <t>-77.0457149</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Calle Las Azucenas / Calle s / n</t>
+          <t>Avenida Húsares de Junín / Jirón Pachacútec</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3071,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>I-1623</t>
+          <t>I-412221</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-12.10858682</t>
+          <t>-11.9831509</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-77.02629095</t>
+          <t>-76.7808835</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Avenida Domingo Orué / Avenida Paseo de la República / Vía Expresa Luis Fernán Bedoya Reyes</t>
+          <t>Avenida Las Cumbres / Calle s / n</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3118,27 +3118,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>I-1625</t>
+          <t>I-411703</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-12.1095906</t>
+          <t>-12.3050753</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-77.026159</t>
+          <t>-76.8211833</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Avenida Paseo de la República / Vía Expresa Luis Fernán Bedoya Reyes</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3165,27 +3165,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>I-16602</t>
+          <t>I-408214</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-12.0267032</t>
+          <t>-12.2971048</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-77.0400082</t>
+          <t>-76.7777361</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Avenida Morro de Arica / Avenida Villacampa</t>
+          <t>Avenida Pampa Pacta / Calle s / n</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3212,27 +3212,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>I-16647</t>
+          <t>I-408169</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-12.275857</t>
+          <t>-12.2945991</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-76.8708196</t>
+          <t>-76.7734677</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Sur / Auxiliar Antigua Panamericana Sur / Calle 27 de Octubre</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3259,27 +3259,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>I-168240</t>
+          <t>I-408166</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-12.1880245</t>
+          <t>-12.2950109</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-76.982814</t>
+          <t>-76.7749667</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Avenida Los Próceres / Pasaje Punta Arena</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3306,27 +3306,27 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>I-168912</t>
+          <t>I-398245</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-11.8813633</t>
+          <t>-12.0631026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-77.0237997</t>
+          <t>-76.9831925</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Calle Los Sauces / Jirón Los Sauces</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3353,22 +3353,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>I-169318</t>
+          <t>I-395918</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-11.8709592</t>
+          <t>-12.0843183</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-77.0200262</t>
+          <t>-77.0647771</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Avenida 12 de Febrero / Avenida Manuel Prado / Calle 12 de Febrero</t>
+          <t>Avenida de La Marina / Calle s / n</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3400,27 +3400,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>I-170467</t>
+          <t>I-395798</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-12.1534238</t>
+          <t>-12.227659</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-77.0197145</t>
+          <t>-76.860808</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Avenida Panamericana Sur / Jirón Deportes</t>
+          <t>Jirón Suspiros / Jirón Comercio</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3447,27 +3447,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>I-17157</t>
+          <t>I-3894</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-12.0577941</t>
+          <t>-12.0934762</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-77.0299528</t>
+          <t>-77.059773</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Avenida Abancay / Jirón Montevideo</t>
+          <t>Avenida Javier Prado Oeste / Jirón Faustino Sanchez Carrión</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3494,27 +3494,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>I-17497</t>
+          <t>I-386877</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-12.0896166</t>
+          <t>-12.0363273</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-77.0585472</t>
+          <t>-77.0595112</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Avenida Faustino Sanchez Carrión / Jirón Comandante Gustavo Jiménez</t>
+          <t>Avenida Morales Duarez / Los Libertadores</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>I-17868</t>
+          <t>I-386460</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-12.0895338</t>
+          <t>-12.1400615</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-77.0662375</t>
+          <t>-77.0280909</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jirón Junín / Jirón Manco Capac</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>I-182645</t>
+          <t>I-382031</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-11.9910562</t>
+          <t>-12.0706926</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-77.0715028</t>
+          <t>-76.7563443</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Avenida Carlos Alberto Izaguirre / Avenida Las Palmeras / Avenida Santiago Antúnez de Mayolo</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3635,22 +3635,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>I-18912</t>
+          <t>I-381730</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-12.0897097</t>
+          <t>-12.0793029</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-77.0658328</t>
+          <t>-77.0482102</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Avenida Javier Prado Oeste / Jirón Junín</t>
+          <t>Avenida Húsares de Junín / Calle s / n</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3682,22 +3682,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>I-197048</t>
+          <t>I-380769</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-12.0661593</t>
+          <t>-12.193123</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-77.0465669</t>
+          <t>-76.9647976</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Jirón Restauración</t>
+          <t>Avenida Los Algarrobos / Avenida Mateo Pumacahua</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3729,27 +3729,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>I-197183</t>
+          <t>I-377326</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-12.0851309</t>
+          <t>-12.2362532</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-77.048899</t>
+          <t>-76.8625071</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Avenida General Salaverry / Avenida Guillermo Prescott / Calle Daniel Olaechea / Calle Luis M. Sanchez Cerro</t>
+          <t>Calle Los Tulipanes / Calle s / n</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3776,27 +3776,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>I-215372</t>
+          <t>I-374816</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-12.0671562</t>
+          <t>-12.040753</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-77.0054809</t>
+          <t>-77.010033</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Avenida México / Calle Santa Rosa / Los Quechuas</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3823,27 +3823,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>I-22303</t>
+          <t>I-374809</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-11.9938117</t>
+          <t>-12.0381385</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-77.0838183</t>
+          <t>-77.0122402</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Avenida Universitaria / Calle 5</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3870,27 +3870,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>I-23581</t>
+          <t>I-374806</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-11.9901501</t>
+          <t>-12.0416127</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-77.0152061</t>
+          <t>-77.0123244</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Avenida Jorge Basadre Oeste / Avenida Las Flores de Primavera</t>
+          <t>Pasaje Santa Rosa / Calle s / n</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3917,27 +3917,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>I-23914</t>
+          <t>I-374804</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-12.0681362</t>
+          <t>-12.0398806</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-77.0482088</t>
+          <t>-77.0115799</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Jirón General Orbegoso</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3964,27 +3964,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>I-243166</t>
+          <t>I-374803</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-11.870633</t>
+          <t>-12.0392702</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-77.0643106</t>
+          <t>-77.010319</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Av. Las Torres / Avenida Industrial / Pasaje Ancash</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4011,22 +4011,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>I-251176</t>
+          <t>I-374707</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-12.1971917</t>
+          <t>-12.0410787</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-76.9992146</t>
+          <t>-76.9632057</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Avenida Alameda Los Horizontes / Avenida Caminos del Inca / Avenida Defensores del Morro / Calle La Fauna</t>
+          <t>Avenida Huancaray / Avenida Los Rosales</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4058,27 +4058,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>I-251268</t>
+          <t>I-374693</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>-12.0732546</t>
+          <t>-12.0595743</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-77.0163699</t>
+          <t>-77.0105044</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Avenida México / Avenida Prolongación Parinacochas</t>
+          <t>Prolongación Avenida San Pablo / Calle s / n</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4105,22 +4105,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>I-251834</t>
+          <t>I-371541</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-11.9831704</t>
+          <t>-12.2323064</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-77.0782501</t>
+          <t>-76.9252791</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Avenida Los Alisos / Avenida Universitaria</t>
+          <t>Avenida Guardia Republicana / Avenida Revolución</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4152,27 +4152,27 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>I-252063</t>
+          <t>I-3551</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-12.0264043</t>
+          <t>-12.0831956</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-77.0547087</t>
+          <t>-76.9704507</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Avenida Eduardo de Habich / Calle Darío Valdizán</t>
+          <t>Avenida Javier Prado Este / Monitor Huáscar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4199,22 +4199,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>I-252229</t>
+          <t>I-355004</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-12.0462803</t>
+          <t>-12.0883472</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-77.0375344</t>
+          <t>-77.004936</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Avenida Emancipación / Avenida Tacna</t>
+          <t>Avenida Javier Prado Este / Calle s / n</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4246,27 +4246,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>I-252324</t>
+          <t>I-352886</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-12.0727086</t>
+          <t>-12.080419</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-76.9928777</t>
+          <t>-77.0580871</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Avenida Circunvalación / Avenida Mariscal Domingo Nieto</t>
+          <t>Avenida Brasil / Calle s / n</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4293,22 +4293,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>I-252463</t>
+          <t>I-352476</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-11.8939769</t>
+          <t>-12.112248</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-77.040941</t>
+          <t>-77.0071234</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Avenida Mariano Condorcanqui / Calle Francisco Wuambo</t>
+          <t>Avenida Angamos Este / Avenida Principal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>I-253050</t>
+          <t>I-352243</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-12.0072012</t>
+          <t>-12.0780242</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-77.0536925</t>
+          <t>-77.0806041</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Avenida Tomás Valle / Avenida Túpac Amaru</t>
+          <t>Avenida de La Marina / Calle Ciclovía La Marina</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4387,22 +4387,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>I-253967</t>
+          <t>I-351782</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-12.0486359</t>
+          <t>-12.0738003</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-77.0592272</t>
+          <t>-77.0361543</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Avenida Naciones Unidas / Jirón Zorritos</t>
+          <t>Avenida Arequipa / Calle s / n</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>I-254646</t>
+          <t>I-347854</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-12.0262176</t>
+          <t>-12.1117776</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-76.920217</t>
+          <t>-77.0032764</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Avenida Nicolás de Ayllón / Victor Raul Haya de la Torre</t>
+          <t>Auxiliar Avenida Angamos Este / Calle s / n</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4481,22 +4481,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>I-257665</t>
+          <t>I-343404</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-12.0610201</t>
+          <t>-12.1507177</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-77.013244</t>
+          <t>-76.9807222</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Avenida 28 de Julio / Avenida Aviación</t>
+          <t>Avenida Los Héroes / Calle s / n</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4528,22 +4528,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>I-257724</t>
+          <t>I-343107</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-12.0840158</t>
+          <t>-12.2027603</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-77.0043057</t>
+          <t>-76.930746</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Avenida Canadá</t>
+          <t>Avenida Juan Velasco Alvarado / Calle s / n</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4575,27 +4575,27 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>I-26393</t>
+          <t>I-342107</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-12.0020323</t>
+          <t>-12.2241983</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-77.0546445</t>
+          <t>-76.919763</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle Las Sandías</t>
+          <t>Avenida 200 Millas / Avenida Pachacútec</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4622,22 +4622,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>I-271942</t>
+          <t>I-337677</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-12.0967554</t>
+          <t>-11.9257052</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-77.0751833</t>
+          <t>-76.9636162</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Calle s / n</t>
+          <t>Avenida Pachacútec / Calle s / n</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4669,27 +4669,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>I-271944</t>
+          <t>I-330244</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-12.097823</t>
+          <t>-12.0778854</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-77.0731326</t>
+          <t>-77.0366102</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Calle s / n</t>
+          <t>Avenida Álvarez de Arenales / Calle Teodoro Cárdenas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4716,22 +4716,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>I-275248</t>
+          <t>I-325897</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-12.0269368</t>
+          <t>-12.0175516</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-77.0334973</t>
+          <t>-77.0021453</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Avenida Felipe Arancibia / Avenida Samuel Alcázar</t>
+          <t>Avenida Piramide del Sol / Avenida Próceres de la Independencia</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4763,22 +4763,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>I-288807</t>
+          <t>I-325186</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-11.845509</t>
+          <t>-12.0121638</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-77.077201</t>
+          <t>-77.0113297</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Avenida Pacífico / Calle s / n</t>
+          <t>Avenida Las Flores de Primavera / Calle s / n</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4810,27 +4810,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>I-298204</t>
+          <t>I-325038</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-12.0873075</t>
+          <t>-12.2640337</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-76.9965065</t>
+          <t>-76.8811439</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Avenida Javier Prado Este / Avenida San Luis</t>
+          <t>Antigua Panamericana Sur / Calle s / n</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4857,27 +4857,27 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>I-300109</t>
+          <t>I-324655</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-12.0623738</t>
+          <t>-11.9881109</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-77.0126242</t>
+          <t>-77.1142804</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Avenida Jaime Bausate y Meza</t>
+          <t>Avenida Alejandro Bertello / Avenida Bertello / Avenida Carlos Alberto Izaguirre</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4904,27 +4904,27 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>I-300767</t>
+          <t>I-324427</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-11.8874896</t>
+          <t>-12.0752235</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-77.0368827</t>
+          <t>-77.0014203</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Avenida Señor de Caudivilla / Calle s / n</t>
+          <t>Avenida San Juan / Calle s / n</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4951,22 +4951,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>I-300936</t>
+          <t>I-324308</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-12.1053013</t>
+          <t>-12.0929543</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-77.0009898</t>
+          <t>-76.9526435</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Jirón Andrés Vesalio</t>
+          <t>Alameda del Corregidor / Jirón Los Bambues</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4998,22 +4998,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>I-302633</t>
+          <t>I-323208</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-12.0660718</t>
+          <t>-12.0590672</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-77.0462395</t>
+          <t>-77.0455612</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Calle s / n</t>
+          <t>Avenida Arica / Calle s / n</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5045,22 +5045,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>I-305207</t>
+          <t>I-322991</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-12.0801623</t>
+          <t>-12.0711584</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-77.0075939</t>
+          <t>-77.0505324</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Calle s / n</t>
+          <t>Avenida Brasil / Avenida Colombia</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5092,22 +5092,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>I-306311</t>
+          <t>I-322764</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-12.1220045</t>
+          <t>-12.0786609</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-77.0056989</t>
+          <t>-77.0569041</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Avenida Manuel Villarán / Avenida de Tomás Marsano / Ruta de buses Tomás Marsano</t>
+          <t>Avenida Brasil / Avenida Francisco Javier Mariátegui</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5139,27 +5139,27 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>I-306732</t>
+          <t>I-322643</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-12.0258357</t>
+          <t>-11.8934426</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-77.0103172</t>
+          <t>-77.0287943</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Avenida Lima / Avenida Próceres de la Independencia</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>I-306848</t>
+          <t>I-322076</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-12.140869</t>
+          <t>-11.9887131</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-76.9488724</t>
+          <t>-77.0568386</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Jirón Almirante Miguel Grau</t>
+          <t>Avenida Carlos Alberto Izaguirre / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5233,27 +5233,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>I-306892</t>
+          <t>I-321183</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-12.041396</t>
+          <t>-11.9421945</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-76.9244058</t>
+          <t>-77.0604067</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Prolongación Javier Prado Este / Calle s / n</t>
+          <t>Avenida Guillermo de la Fuente / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -5280,22 +5280,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>I-308127</t>
+          <t>I-321175</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-11.9861505</t>
+          <t>-11.9286255</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-77.0722492</t>
+          <t>-77.0560583</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Avenida José Santos Chocano / Avenida Las Palmeras</t>
+          <t>Avenida El Retablo / Avenida Micaela Bastidas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5327,22 +5327,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>I-309715</t>
+          <t>I-321047</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-12.0286877</t>
+          <t>-11.8847962</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-76.9997477</t>
+          <t>-77.0234187</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Calle Malecón de la Amistad</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>I-31211</t>
+          <t>I-320949</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-12.039906</t>
+          <t>-12.0841034</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-77.0302112</t>
+          <t>-77.0390185</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Avenida Francisco Pizarro / Jirón Cajamarca / Jirón Paita</t>
+          <t>Avenida General César Canevaro / Jirón Almirante Martin Guisse</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5421,22 +5421,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>I-31420</t>
+          <t>I-31793</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-12.0367729</t>
+          <t>-12.0503571</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-77.0310944</t>
+          <t>-77.047358</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Avenida Prolongación Tacna / Jirón Chira</t>
+          <t>Jirón Jorge Chávez / Jirón Zorritos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>I-314272</t>
+          <t>I-316876</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-12.0351922</t>
+          <t>-11.9831325</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-77.0298884</t>
+          <t>-77.0799259</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Avenida Prolongación Tacna / Calle s / n</t>
+          <t>Avenida Los Alisos / Calle s / n</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5515,22 +5515,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>I-314877</t>
+          <t>I-316738</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-12.0541397</t>
+          <t>-12.0074429</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-77.0615896</t>
+          <t>-77.0823455</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Avenida Naciones Unidas / Avenida Prolongación Arica</t>
+          <t>Avenida Universitaria / Calle s / n</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5562,22 +5562,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>I-315973</t>
+          <t>I-316381</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-12.0134871</t>
+          <t>-12.1056964</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-77.0871845</t>
+          <t>-77.0176777</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Avenida 12 de Octubre / Avenida El Olivar / Avenida Tomás Valle / Jirón Toribio de Luzuriaga</t>
+          <t>Avenida de Tomás Marsano / Calle s / n</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5609,22 +5609,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>I-316381</t>
+          <t>I-315973</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-12.1056964</t>
+          <t>-12.0134871</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-77.0176777</t>
+          <t>-77.0871845</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Avenida de Tomás Marsano / Calle s / n</t>
+          <t>Avenida 12 de Octubre / Avenida El Olivar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5656,22 +5656,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>I-316738</t>
+          <t>I-314877</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-12.0074429</t>
+          <t>-12.0541397</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-77.0823455</t>
+          <t>-77.0615896</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Avenida Universitaria / Calle s / n</t>
+          <t>Avenida Naciones Unidas / Avenida Prolongación Arica</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5703,22 +5703,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>I-316876</t>
+          <t>I-314272</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-11.9831325</t>
+          <t>-12.0351922</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-77.0799259</t>
+          <t>-77.0298884</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Avenida Los Alisos / Calle s / n</t>
+          <t>Avenida Prolongación Tacna / Calle s / n</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5750,22 +5750,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>I-31793</t>
+          <t>I-31420</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-12.0503571</t>
+          <t>-12.0367729</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-77.047358</t>
+          <t>-77.0310944</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Jirón Jorge Chávez / Jirón Zorritos</t>
+          <t>Avenida Prolongación Tacna / Jirón Chira</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>I-320949</t>
+          <t>I-31211</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-12.0841034</t>
+          <t>-12.039906</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-77.0390185</t>
+          <t>-77.0302112</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Avenida General César Canevaro / Jirón Almirante Martin Guisse</t>
+          <t>Avenida Francisco Pizarro / Jirón Cajamarca / Jirón Paita</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5844,22 +5844,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>I-321047</t>
+          <t>I-311293</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-11.8847962</t>
+          <t>-12.0462004</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-77.0234187</t>
+          <t>-76.9440121</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Avenida Nicolás de Ayllón / Calle s / n</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5891,22 +5891,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>I-321175</t>
+          <t>I-309715</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-11.9286255</t>
+          <t>-12.0286877</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-77.0560583</t>
+          <t>-76.9997477</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Avenida El Retablo / Avenida Micaela Bastidas</t>
+          <t>Avenida José Carlos Mariátegui / Calle Malecón de la Amistad</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5938,27 +5938,27 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>I-321183</t>
+          <t>I-308127</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-11.9421945</t>
+          <t>-11.9861505</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-77.0604067</t>
+          <t>-77.0722492</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Avenida Guillermo de la Fuente / Avenida Universitaria</t>
+          <t>Avenida José Santos Chocano / Avenida Las Palmeras</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5985,22 +5985,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>I-322076</t>
+          <t>I-306892</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-11.9887131</t>
+          <t>-12.041396</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-77.0568386</t>
+          <t>-76.9244058</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Avenida Carlos Alberto Izaguirre / Avenida Túpac Amaru / María Parado de Bellido</t>
+          <t>Prolongación Javier Prado Este / Calle s / n</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6032,22 +6032,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>I-322643</t>
+          <t>I-306848</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-11.8934426</t>
+          <t>-12.140869</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-77.0287943</t>
+          <t>-76.9488724</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Avenida Señor de Caudivilla / Avenida Túpac Amaru</t>
+          <t>Avenida José Carlos Mariátegui / Calle s / n</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6079,27 +6079,27 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>I-323208</t>
+          <t>I-306732</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-12.0590672</t>
+          <t>-12.0258357</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-77.0455612</t>
+          <t>-77.0103172</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Avenida Arica / Calle s / n</t>
+          <t>Avenida Próceres de la Independencia / Calle s / n</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6126,27 +6126,27 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>I-324308</t>
+          <t>I-306730</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-12.0929543</t>
+          <t>-12.0740921</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-76.9526435</t>
+          <t>-77.0530194</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Alameda del Corregidor / Jirón Los Bambues</t>
+          <t>Avenida Afranio de Mello Franco / Avenida Brasil</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6173,22 +6173,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>I-324655</t>
+          <t>I-306311</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-11.9881109</t>
+          <t>-12.1220045</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-77.1142804</t>
+          <t>-77.0056989</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Avenida Alejandro Bertello / Avenida Bertello / Avenida Carlos Alberto Izaguirre</t>
+          <t>Avenida Manuel Villarán / Avenida de Tomás Marsano</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6220,22 +6220,22 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>I-325186</t>
+          <t>I-305207</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-12.0121638</t>
+          <t>-12.0801623</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-77.0113297</t>
+          <t>-77.0075939</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Avenida Las Flores de Primavera / Avenida Los Tusilagos Oeste</t>
+          <t>Avenida Aviación / Calle s / n</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6267,27 +6267,27 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>I-325897</t>
+          <t>I-30298</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-12.0175516</t>
+          <t>-11.8654246</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-77.0021453</t>
+          <t>-77.078941</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Avenida Piramide del Sol / Avenida Próceres de la Independencia / Proceres de la Independencia</t>
+          <t>Avenida Ricardo Palma / Avenida Sucre</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>I-330244</t>
+          <t>I-302633</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-12.0778854</t>
+          <t>-12.0660718</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-77.0366102</t>
+          <t>-77.0462395</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Avenida Álvarez de Arenales / Calle Teodoro Cárdenas</t>
+          <t>Avenida Brasil / Calle s / n</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6361,27 +6361,27 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>I-342107</t>
+          <t>I-300936</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-12.2241983</t>
+          <t>-12.1053013</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-76.919763</t>
+          <t>-77.0009898</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Avenida 200 Millas / Avenida Pachacútec</t>
+          <t>Avenida Aviación / Calle s / n</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6408,22 +6408,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>I-343107</t>
+          <t>I-300767</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-12.2027603</t>
+          <t>-11.8874896</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-76.930746</t>
+          <t>-77.0368827</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Avenida Juan Velasco Alvarado / Avenida Pachacútec</t>
+          <t>Avenida Señor de Caudivilla / Calle s / n</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6455,27 +6455,27 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>I-343404</t>
+          <t>I-300109</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-12.1507177</t>
+          <t>-12.0623738</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-76.9807222</t>
+          <t>-77.0126242</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Avenida Los Héroes / Avenida Los Lirios / Paradero Atocongo</t>
+          <t>Avenida Aviación / Avenida Jaime Bausate y Meza</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6502,27 +6502,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>I-347854</t>
+          <t>I-298204</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-12.1117776</t>
+          <t>-12.0873075</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-77.0032764</t>
+          <t>-76.9965065</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Angamos Este / Avenida Angamos Este / Avenida Ricardo Malachowsky</t>
+          <t>Avenida Javier Prado Este / Avenida San Luis</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6549,22 +6549,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>I-351782</t>
+          <t>I-288807</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-12.0738003</t>
+          <t>-11.845509</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-77.0361543</t>
+          <t>-77.077201</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Avenida Arequipa / Calle s / n</t>
+          <t>Avenida Pacífico / Calle s / n</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6596,22 +6596,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>I-352476</t>
+          <t>I-275248</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-12.112248</t>
+          <t>-12.0269368</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-77.0071234</t>
+          <t>-77.0334973</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Avenida Angamos Este / Avenida José Gálvez Barrenechea / Avenida Principal</t>
+          <t>Avenida Samuel Alcázar / Calle s / n</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6643,27 +6643,27 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>I-352886</t>
+          <t>I-2737</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-12.080419</t>
+          <t>-12.1131961</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-77.0580871</t>
+          <t>-77.0255271</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Calle s / n</t>
+          <t>Avenida General Recavarren / Avenida Paseo de la República</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6690,27 +6690,27 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>I-371541</t>
+          <t>I-271944</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-12.2323064</t>
+          <t>-12.097823</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-76.9252791</t>
+          <t>-77.0731326</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Avenida Guardia Republicana / Avenida Revolución</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6737,22 +6737,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>I-374707</t>
+          <t>I-271942</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-12.0410787</t>
+          <t>-12.0967554</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-76.9632057</t>
+          <t>-77.0751833</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Avenida Huancaray / Avenida Los Rosales</t>
+          <t>Circuito de Playas / Calle s / n</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6784,22 +6784,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>I-380769</t>
+          <t>I-26393</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-12.193123</t>
+          <t>-12.0020323</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-76.9647976</t>
+          <t>-77.0546445</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Avenida Los Algarrobos / Avenida Mateo Pumacahua</t>
+          <t>Avenida Túpac Amaru / Calle Las Sandías</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>I-386460</t>
+          <t>I-257724</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-12.1400615</t>
+          <t>-12.0840158</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-77.0280909</t>
+          <t>-77.0043057</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Quebrada de Armendariz</t>
+          <t>Avenida Aviación / Avenida Canadá</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6878,27 +6878,27 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>I-386877</t>
+          <t>I-257665</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-12.0363273</t>
+          <t>-12.0610201</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-77.0595112</t>
+          <t>-77.013244</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Avenida Morales Duarez / Los Libertadores / Vía Expresa Línea Amarilla</t>
+          <t>Avenida 28 de Julio / Calle s / n</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6925,22 +6925,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>I-431746</t>
+          <t>I-254646</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-12.1521436</t>
+          <t>-12.0262176</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-77.0246022</t>
+          <t>-76.920217</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Calle s / n</t>
+          <t>Avenida José Carlos Mariátegui / Avenida Nicolás de Ayllón</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6972,27 +6972,27 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>I-436514</t>
+          <t>I-253967</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-11.9742495</t>
+          <t>-12.0486359</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-76.7689808</t>
+          <t>-77.0592272</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Avenida Malecón Manco Cápac / Calle s / n</t>
+          <t>Jirón Zorritos / Calle s / n</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7019,27 +7019,27 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>I-442184</t>
+          <t>I-253050</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-12.2213482</t>
+          <t>-12.0072012</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-76.9202054</t>
+          <t>-77.0536925</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Avenida 6 / Avenida Pachacútec</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7066,22 +7066,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>I-4477</t>
+          <t>I-252463</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-12.13407441</t>
+          <t>-11.8939769</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-77.02055953</t>
+          <t>-77.040941</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Vía Expresa Luis Fernán Bedoya Reyes / Calle s / n</t>
+          <t>Avenida Mariano Condorcanqui / Calle Francisco Wuambo</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>I-4578</t>
+          <t>I-252351</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-12.1156861</t>
+          <t>-12.0828739</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-77.0102719</t>
+          <t>-77.0670971</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Alejandro Deustua / Avenida de Tomás Marsano / República del Salvador / Ruta de buses Tomás Marsano</t>
+          <t>Avenida Antonio José de Sucre / Calle s / n</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7160,22 +7160,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>I-4986</t>
+          <t>I-252324</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-11.9886777</t>
+          <t>-12.0727086</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-77.0808392</t>
+          <t>-76.9928777</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Avenida Los Olivos / Avenida Universitaria</t>
+          <t>Avenida Circunvalación / Avenida Mariscal Domingo Nieto</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>I-5065</t>
+          <t>I-252229</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-11.9525292</t>
+          <t>-12.0462803</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-77.0514694</t>
+          <t>-77.0375344</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Avenida 22 de Agosto / Avenida Túpac Amaru</t>
+          <t>Avenida Emancipación / Avenida Tacna</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>I-511125</t>
+          <t>I-252063</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-12.0263356</t>
+          <t>-12.0264043</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-76.8923119</t>
+          <t>-77.0547087</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Avenida Alfonso Ugarte / Calle s / n</t>
+          <t>Avenida Eduardo de Habich / Calle Darío Valdizán</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7301,22 +7301,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>I-588266</t>
+          <t>I-251834</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-12.1544387</t>
+          <t>-11.9831704</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-76.8692864</t>
+          <t>-77.0782501</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Avenida Víctor Malásquez / Calle Las Rosas</t>
+          <t>Avenida Los Alisos / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7348,22 +7348,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>I-6253</t>
+          <t>I-251268</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-12.0627362</t>
+          <t>-12.0732546</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-77.0437682</t>
+          <t>-77.0163699</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Jirón Don Bosco</t>
+          <t>Avenida México / Avenida Prolongación Parinacochas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7395,22 +7395,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>I-681300</t>
+          <t>I-251203</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-12.1819848</t>
+          <t>-12.1837938</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-76.9423705</t>
+          <t>-77.007998</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Avenida Pachacútec / Calle Albino Torres</t>
+          <t>Avenida Prolongación Paseo de la República / Calle s / n</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7442,22 +7442,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>I-6823</t>
+          <t>I-251176</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-12.1014778</t>
+          <t>-12.1971917</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-77.0667181</t>
+          <t>-76.9992146</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Calle s / n</t>
+          <t>Avenida Alameda Los Horizontes / Avenida Defensores del Morro</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7489,22 +7489,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>I-736851</t>
+          <t>I-243166</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-12.0056996</t>
+          <t>-11.870633</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-76.8642115</t>
+          <t>-77.0643106</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Avenida Ramiro Prialé / Calle Los Sauces</t>
+          <t>Av. Las Torres / Pasaje Ancash</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7536,27 +7536,27 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>I-748018</t>
+          <t>I-23914</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-12.0861374</t>
+          <t>-12.0681362</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-77.0355273</t>
+          <t>-77.0482088</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Avenida Álvarez de Arenales / Calle s / n</t>
+          <t>Avenida Brasil / Jirón General Orbegoso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7583,22 +7583,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>I-748465</t>
+          <t>I-23581</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-12.091591</t>
+          <t>-11.9901501</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-77.008457</t>
+          <t>-77.0152061</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Avenida Guardia Civil / Calle s / n</t>
+          <t>Avenida Jorge Basadre Oeste / Avenida Las Flores de Primavera</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7630,27 +7630,27 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>I-749340</t>
+          <t>I-22303</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-12.1675915</t>
+          <t>-11.9938117</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>-76.9784144</t>
+          <t>-77.0838183</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Avenida Alipio Ponce / Avenida Pedro Miotta</t>
+          <t>Avenida Universitaria / Calle 5</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7677,22 +7677,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>I-77065</t>
+          <t>I-215372</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-11.9162314</t>
+          <t>-12.0671562</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>-77.0411424</t>
+          <t>-77.0054809</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle San Juan Bautista</t>
+          <t>Avenida México / Los Quechuas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7724,27 +7724,27 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>I-777501</t>
+          <t>I-2016</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-12.0670326</t>
+          <t>-11.9515877</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>-76.9969118</t>
+          <t>-76.988289</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Circunvalación / Avenida Pablo Patron / Calle Leonidas La Serre</t>
+          <t>Avenida José Carlos Mariátegui / Calle s / n</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7771,27 +7771,27 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>I-783659</t>
+          <t>I-1997</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-12.0702149</t>
+          <t>-12.0830465</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>-76.9944527</t>
+          <t>-77.0457554</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Circunvalación / Calle s / n</t>
+          <t>Jirón Belisario Flores / Jirón Pachacútec</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7818,22 +7818,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>I-8773</t>
+          <t>I-197183</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-12.0766035</t>
+          <t>-12.0851309</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>-76.9961052</t>
+          <t>-77.048899</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Avenida Del Aire / Jirón Rio Chira</t>
+          <t>Avenida General Salaverry / Avenida Guillermo Prescott / Calle Daniel Olaechea</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7865,22 +7865,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>I-88778</t>
+          <t>I-197048</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-11.927936</t>
+          <t>-12.0661593</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>-77.0522899</t>
+          <t>-77.0465669</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Avenida Universitaria / Calle José Santos Atahuaipa</t>
+          <t>Avenida Brasil / Jirón Restauración</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7912,22 +7912,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>I-89306</t>
+          <t>I-18912</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-11.930191</t>
+          <t>-12.0897097</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-77.0534599</t>
+          <t>-77.0658328</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Avenida Micaela Bastidas / Avenida Universitaria</t>
+          <t>Avenida Brasil / Jirón Junín</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>I-89490</t>
+          <t>I-182645</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-11.9372754</t>
+          <t>-11.9910562</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>-77.0489711</t>
+          <t>-77.0715028</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Los Cactus</t>
+          <t>Avenida Carlos Alberto Izaguirre / Calle s / n</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8006,22 +8006,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>I-92193</t>
+          <t>I-17868</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-12.2526713</t>
+          <t>-12.0895338</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-76.897967</t>
+          <t>-77.0662375</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Sur / Jirón Los Olivos</t>
+          <t>Jirón Junín / Jirón Manco Capac</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8053,27 +8053,27 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>I-93330</t>
+          <t>I-175849</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-12.1950692</t>
+          <t>-11.9666848</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>-77.0014774</t>
+          <t>-76.7415894</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Avenida Caminos del Inca / Jirón Leoncio Prado</t>
+          <t>Avenida California / Calle s / n</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8100,22 +8100,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>I-93465</t>
+          <t>I-17497</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-12.0419083</t>
+          <t>-12.0896166</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>-76.9654322</t>
+          <t>-77.0585472</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Avenida Huancaray / Avenida Santa Rosa / Calle Chavín</t>
+          <t>Avenida Faustino Sanchez Carrión / Jirón Comandante Gustavo Jiménez</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8147,22 +8147,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>I-95315</t>
+          <t>I-172771</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-12.1670486</t>
+          <t>-12.2964243</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>-76.949869</t>
+          <t>-76.8509571</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Avenida El Triunfo / Avenida Nicolás de Piérola</t>
+          <t>Jirón 7 de Junio / Calle s / n</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8194,22 +8194,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>I-97671</t>
+          <t>I-17157</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-11.8972601</t>
+          <t>-12.0577941</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>-77.030015</t>
+          <t>-77.0299528</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Avenida Abancay / Jirón Montevideo</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8241,22 +8241,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>I-98356</t>
+          <t>I-170467</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-12.1512504</t>
+          <t>-12.1534238</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>-76.9792259</t>
+          <t>-77.0197145</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Avenida Los Héroes / Calle Las Fresas</t>
+          <t>Avenida Panamericana Sur / Jirón Deportes</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8288,22 +8288,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>I-113498</t>
+          <t>I-169318</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-11.9630517</t>
+          <t>-11.8709592</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>-77.0789858</t>
+          <t>-77.0200262</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Avenida A / Calle s / n</t>
+          <t>Avenida 12 de Febrero / Avenida Manuel Prado / Calle 12 de Febrero</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8335,27 +8335,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>I-136729</t>
+          <t>I-168912</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-12.1453892</t>
+          <t>-11.8813633</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>-76.83216</t>
+          <t>-77.0237997</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Avenida Luis Felipe de las Casas Grieve / Calle s / n</t>
+          <t>Avenida Camino Real / Calle Los Sauces</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8382,22 +8382,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>I-136879</t>
+          <t>I-168240</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-11.863619</t>
+          <t>-12.1880245</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>-77.0081562</t>
+          <t>-76.982814</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Pasaje Punta Arena / Calle s / n</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8429,27 +8429,27 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>I-137628</t>
+          <t>I-16822</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-11.9987694</t>
+          <t>-11.9676645</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>-76.9264525</t>
+          <t>-76.7429975</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Avenida Las Torres / Calle s / n</t>
+          <t>Avenida Nicolás Ayllón / Calle s / n</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8476,27 +8476,27 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>I-137716</t>
+          <t>I-16821</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-12.252992</t>
+          <t>-11.9671086</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>-76.8937177</t>
+          <t>-76.7419699</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Sur / Calle s / n</t>
+          <t>Avenida California / Avenida Nicolás Ayllón</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8523,22 +8523,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>I-138392</t>
+          <t>I-16647</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-12.0347723</t>
+          <t>-12.275857</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>-76.9314249</t>
+          <t>-76.8708196</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Avenida Los Ángeles / Calle s / n</t>
+          <t>Antigua Panamericana Sur / Calle 27 de Octubre</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8570,22 +8570,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>I-156461</t>
+          <t>I-16602</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-11.8739956</t>
+          <t>-12.0267032</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>-77.0603979</t>
+          <t>-77.0400082</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Avenida San Juan de Villa / Calle s / n</t>
+          <t>Avenida Morro de Arica / Avenida Villacampa</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8617,27 +8617,27 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>I-398245</t>
+          <t>I-1625</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-12.0631026</t>
+          <t>-12.1095906</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>-76.9831925</t>
+          <t>-77.026159</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Avenida Nicolás de Ayllón / Calle s / n</t>
+          <t>Vía Expresa Luis Fernán Bedoya Reyes / Calle s / n</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8664,22 +8664,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>I-251203</t>
+          <t>I-1623</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-12.1837938</t>
+          <t>-12.10858682</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>-77.007998</t>
+          <t>-77.02629095</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Avenida Prolongación Paseo de la República / Calle s / n</t>
+          <t>Vía Expresa Luis Fernán Bedoya Reyes / Calle s / n</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>I-311293</t>
+          <t>I-157768</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-12.0462004</t>
+          <t>-11.8213548</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>-76.9440121</t>
+          <t>-77.103016</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Avenida Nicolás de Ayllón / Calle s / n</t>
+          <t>Calle Los Geranios / Calle Las Azucenas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8758,27 +8758,27 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>I-92028</t>
+          <t>I-156461</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-11.9734721</t>
+          <t>-11.8739956</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>-76.7649977</t>
+          <t>-77.0603979</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Juan de Villa / Calle s / n</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8805,22 +8805,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>I-325038</t>
+          <t>I-156310</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-12.2640337</t>
+          <t>-11.9694561</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>-76.8811439</t>
+          <t>-76.937414</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Antigua Panamericana Sur / Calle s / n</t>
+          <t>Avenida Unión Jicamarca / Calle Bolognesi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>I-355004</t>
+          <t>I-156039</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-12.0883472</t>
+          <t>-12.0292721</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>-77.004936</t>
+          <t>-77.0178999</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Avenida Javier Prado Este / Calle s / n</t>
+          <t>Avenida Principal / Avenida Rímac</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8899,27 +8899,27 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>I-382031</t>
+          <t>I-155686</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-12.0706926</t>
+          <t>-12.1158919</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>-76.7563443</t>
+          <t>-76.8732456</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Víctor Malásquez / Calle s / n</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8946,22 +8946,22 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>I-687369</t>
+          <t>I-1524</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-12.0778822</t>
+          <t>-11.9754451</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>-76.8566454</t>
+          <t>-77.0596483</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Metropolitana / Santa Ligia</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8993,27 +8993,27 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>I-430050</t>
+          <t>I-152334</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-12.0903621</t>
+          <t>-12.0706369</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>-76.8560453</t>
+          <t>-77.03157845</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Avenida Santa Rosa / Calle s / n</t>
+          <t>Avenida Paseo de la República / Calle Vía Expresa Luis Fernán Bedoya Reyes</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9040,22 +9040,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>I-377326</t>
+          <t>I-15204</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-12.2362532</t>
+          <t>-12.1805641</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>-76.8625071</t>
+          <t>-76.9436296</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Calle Los Tulipanes / Calle s / n</t>
+          <t>Avenida Pachacútec / Óvalo 26 de Noviembre</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9087,22 +9087,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>I-381730</t>
+          <t>I-1519</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-12.0793029</t>
+          <t>-12.0319059</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>-77.0482102</t>
+          <t>-77.075132</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Avenida Húsares de Junín / Calle s / n</t>
+          <t>Avenida Perú / Calle s / n</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9134,27 +9134,27 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>I-408214</t>
+          <t>I-151221</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-12.2971048</t>
+          <t>-12.0316811</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>-76.7777361</t>
+          <t>-76.9501879</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Avenida Pampa Pacta / Calle s / n</t>
+          <t>Avenida de La Cultura / Calle 11</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9181,27 +9181,27 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>I-412221</t>
+          <t>I-148244</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-11.9831509</t>
+          <t>-12.0819895</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>-76.7808835</t>
+          <t>-76.928718</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Avenida Las Cumbres / Calle s / n</t>
+          <t>Avenida 7 / Calle s / n</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9228,27 +9228,27 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>I-421732</t>
+          <t>I-145496</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-12.2382054</t>
+          <t>-12.2448713</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>-76.8606208</t>
+          <t>-76.9202892</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Avenida Camino Real / Calle s / n</t>
+          <t>Calle 20 / Calle s / n</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9275,22 +9275,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>I-431785</t>
+          <t>I-145305</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-12.0063421</t>
+          <t>-12.1802321</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>-76.8302505</t>
+          <t>-76.9979157</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Avenida Los Incas / Calle s / n</t>
+          <t>Avenida Guardia Civil Sur / Calle Los Meteoros</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9322,27 +9322,27 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>I-792383</t>
+          <t>I-143121</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-12.0853501</t>
+          <t>-12.2245075</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>-76.8889466</t>
+          <t>-76.938757</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida José Carlos Mariátegui / Calle E</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9369,27 +9369,27 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>I-6117</t>
+          <t>I-142706</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-12.162338</t>
+          <t>-12.1898993</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>-77.0259681</t>
+          <t>-77.0065322</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Calle s / n</t>
+          <t>Avenida Defensores del Morro / Calle Rinconada de Villa</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -9416,27 +9416,27 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>I-408166</t>
+          <t>I-138392</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-12.2950109</t>
+          <t>-12.0347723</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>-76.7749667</t>
+          <t>-76.9314249</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Los Ángeles / Calle s / n</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9463,27 +9463,27 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>I-408169</t>
+          <t>I-138197</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-12.2945991</t>
+          <t>-12.15943151</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>-76.7734677</t>
+          <t>-76.95873889</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Miguel Iglesias / Jirón Túpac Amaru</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9510,27 +9510,27 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>I-574545</t>
+          <t>I-138062</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-12.3009928</t>
+          <t>-12.1616654</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>-76.7916584</t>
+          <t>-76.9650321</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Guillermo Billinghurst / Valentín Espejo</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9557,22 +9557,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>I-574584</t>
+          <t>I-137799</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-12.300693</t>
+          <t>-12.1227253</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>-76.7893688</t>
+          <t>-76.8155333</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Nueva Toledo / Calle Pacayal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9604,27 +9604,27 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>I-374816</t>
+          <t>I-137776</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-12.040753</t>
+          <t>-12.2355103</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>-77.010033</t>
+          <t>-76.9162344</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Separadora Industrial / Pasaje 9</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9651,27 +9651,27 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>I-374693</t>
+          <t>I-137716</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-12.0595743</t>
+          <t>-12.252992</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>-77.0105044</t>
+          <t>-76.8937177</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Prolongación Avenida San Pablo / Calle s / n</t>
+          <t>Antigua Panamericana Sur / Calle s / n</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9698,27 +9698,27 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>I-374803</t>
+          <t>I-137628</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-12.0392702</t>
+          <t>-11.9987694</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>-77.010319</t>
+          <t>-76.9264525</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Las Torres / Calle s / n</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9745,22 +9745,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>I-374804</t>
+          <t>I-137012</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-12.0398806</t>
+          <t>-11.9755819</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>-77.0115799</t>
+          <t>-76.772891</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Malecón Manco Cápac / Calle Los Naranjos</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9792,27 +9792,27 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>I-374806</t>
+          <t>I-136879</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-12.0416127</t>
+          <t>-11.863619</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>-77.0123244</t>
+          <t>-77.0081562</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Pasaje Santa Rosa / Calle s / n</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9839,27 +9839,27 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>I-761437</t>
+          <t>I-136729</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-12.0687618</t>
+          <t>-12.1453892</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>-77.0484618</t>
+          <t>-76.83216</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Calle s / n</t>
+          <t>Avenida Luis Felipe de las Casas Grieve / Calle s / n</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9886,22 +9886,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>I-99134</t>
+          <t>I-1363</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-12.0887043</t>
+          <t>-12.0376999</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>-76.8699667</t>
+          <t>-77.0429004</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Los Constructores / Calle s / n</t>
+          <t>Circunvalación / Calle s / n</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9933,27 +9933,27 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>I-583974</t>
+          <t>I-135791</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-12.0846493</t>
+          <t>-12.0358187</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>-76.8634587</t>
+          <t>-76.9996691</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Ferrocarril / Los Zorzales</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -9980,27 +9980,27 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>I-1997</t>
+          <t>I-135778</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-12.0830465</t>
+          <t>-12.07610484</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>-77.0457554</t>
+          <t>-77.02762207</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Jirón Belisario Flores / Jirón Pachacútec</t>
+          <t>Avenida Manco Cápac / Avenida México</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10027,27 +10027,27 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>I-4210</t>
+          <t>I-133645</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-12.0795977</t>
+          <t>-12.059654</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>-77.0457149</t>
+          <t>-77.0298397</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Avenida Húsares de Junín / Jirón Pachacútec</t>
+          <t>Avenida Manco Cápac / Calle s / n</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10074,22 +10074,22 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>I-4212</t>
+          <t>I-1335</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-12.0754842</t>
+          <t>-12.0437571</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>-77.0439545</t>
+          <t>-77.0433255</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Jirón Huayna Cápac / Calle s / n</t>
+          <t>Avenida Alfonso Ugarte / Plaza Ramón Castilla</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10121,27 +10121,27 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>I-553657</t>
+          <t>I-132628</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-12.0970493</t>
+          <t>-12.0913633</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>-77.0715608</t>
+          <t>-77.0673503</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Avenida Brasil / Avenida Del Ejército</t>
+          <t>Avenida Brasil / Jirón San Martín</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10168,27 +10168,27 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>I-3894</t>
+          <t>I-127869</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-12.0934762</t>
+          <t>-12.2187471</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>-77.059773</t>
+          <t>-76.9399948</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Avenida Javier Prado Oeste / Jirón Faustino Sanchez Carrión</t>
+          <t>Avenida Bolívar / Avenida Micaela Bastidas</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10215,22 +10215,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>I-252351</t>
+          <t>I-127791</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-12.0828739</t>
+          <t>-12.197277</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>-77.0670971</t>
+          <t>-76.9529804</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Avenida Antonio José de Sucre / Avenida de La Marina</t>
+          <t>Avenida Micaela Bastidas / Calle 2</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10262,27 +10262,27 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>I-272285</t>
+          <t>I-127177</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-12.0706968</t>
+          <t>-12.0607028</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>-77.0779947</t>
+          <t>-77.0588482</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Avenida Universitaria / Calle s / n</t>
+          <t>Avenida Tingo María / Jirón Chamaya</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10309,27 +10309,27 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>I-299219</t>
+          <t>I-125829</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-12.0812194</t>
+          <t>-11.9636651</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>-77.0663975</t>
+          <t>-77.0925209</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Avenida Antonio José de Sucre / Jirón Cabo Nicolás Gutarra</t>
+          <t>Avenida Tantamayo / Calle 23</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10356,27 +10356,27 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>I-411703</t>
+          <t>I-124607</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-12.3050753</t>
+          <t>-11.9230559</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>-76.8211833</t>
+          <t>-77.0767791</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle 16 / Calle s / n</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10403,27 +10403,27 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>I-1335</t>
+          <t>I-122923</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-12.0437571</t>
+          <t>-12.0551807</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>-77.0433255</t>
+          <t>-77.0040035</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Avenida Alfonso Ugarte / Avenida República de Argentina / Metropolitano / Plaza Ramón Castilla</t>
+          <t>Avenida Mártir José Olaya / El Agustino / Santa Isabel</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10450,27 +10450,27 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>I-374809</t>
+          <t>I-122328</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-12.0381385</t>
+          <t>-11.912586</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>-77.0122402</t>
+          <t>-77.0036922</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Revolución / Jirón Santa Rosa</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10497,27 +10497,27 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>I-6809</t>
+          <t>I-121622</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-12.0663389</t>
+          <t>-11.9949537</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>-77.0542325</t>
+          <t>-77.0769602</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Avenida Mariano Cornejo / Jirón Loreto / Jirón Pedro Ruiz Gallo / Ovalo Breña</t>
+          <t>Avenida Santiago Antúnez de Mayolo / Hernandaz</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10544,27 +10544,27 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>I-1524</t>
+          <t>I-121247</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-11.9754451</t>
+          <t>-11.9917882</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>-77.0596483</t>
+          <t>-77.0751161</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Avenida Metropolitana / Santa Ligia</t>
+          <t>Avenida Carlos Alberto Izaguirre / Conococha</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10591,27 +10591,27 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>I-3551</t>
+          <t>I-120958</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-12.0831956</t>
+          <t>-11.9958872</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>-76.9704507</t>
+          <t>-77.0834199</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Avenida Javier Prado Este / Monitor Huáscar</t>
+          <t>Avenida Santiago Antúnez de Mayolo / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10638,27 +10638,27 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>I-6637</t>
+          <t>I-120450</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-12.0781154</t>
+          <t>-12.0062929</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>-77.0107659</t>
+          <t>-77.0822386</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Avenida Nicolás Arriola / Óvalo de Arriola</t>
+          <t>Avenida Angélica Gamarra / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10685,27 +10685,27 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>I-1363</t>
+          <t>I-119925</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-12.0376999</t>
+          <t>-11.9332644</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>-77.0429004</t>
+          <t>-76.9688159</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Circunvalación / Calle s / n</t>
+          <t>Avenida Fernando Wiesse / Avenida Pachacútec / Jirón Mar del Norte</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10732,27 +10732,27 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>I-2016</t>
+          <t>I-117769</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-11.9515877</t>
+          <t>-11.9615295</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>-76.988289</t>
+          <t>-76.9828702</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Avenida José Carlos Mariátegui / Calle s / n</t>
+          <t>Avenida Héroes del Cenepa Oeste / Los Geologos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10779,27 +10779,27 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>I-8770</t>
+          <t>I-116632</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-12.075317</t>
+          <t>-11.9934576</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>-76.9912288</t>
+          <t>-77.0565083</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Circunvalación / Jirón Trinidad</t>
+          <t>Cesar Vallejo / María Parado de Bellido</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10826,27 +10826,27 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>I-324427</t>
+          <t>I-115963</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-12.0752235</t>
+          <t>-11.9646572</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>-77.0014203</t>
+          <t>-77.0552137</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Avenida San Juan / Calle s / n</t>
+          <t>Jirón Miguel Grau / Calle s / n</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10873,27 +10873,27 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>I-2737</t>
+          <t>I-114905</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>-12.1131961</t>
+          <t>-11.970241</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>-77.0255271</t>
+          <t>-77.0059095</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Avenida General Recavarren / Avenida Paseo de la República</t>
+          <t>Avenida Canto Grande / Avenida Las Flores / Lloque Llupanqui</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10920,27 +10920,27 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>I-15204</t>
+          <t>I-114053</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-12.1805641</t>
+          <t>-11.9539257</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>-76.9436296</t>
+          <t>-77.0516219</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Avenida Pachacútec / Avenida Tahuantinsuyo / Óvalo 26 de Noviembre</t>
+          <t>Avenida Santa Cruz / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10967,27 +10967,27 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>I-2036</t>
+          <t>I-113498</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-12.0096538</t>
+          <t>-11.9630517</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>-76.8223164</t>
+          <t>-77.0789858</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Avenida 15 de Julio / Avenida Andrés Avelino Cáceres</t>
+          <t>Avenida A / Calle s / n</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11014,27 +11014,27 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>I-383461</t>
+          <t>I-113444</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-12.0601531</t>
+          <t>-11.9719159</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>-76.9667199</t>
+          <t>-77.0755251</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Avenida Los Frutales / Calle s / n</t>
+          <t>Avenida Río Marañon / Avenida Universitaria</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11061,27 +11061,27 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>I-383463</t>
+          <t>I-109980</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-12.0591454</t>
+          <t>-12.0356324</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>-76.9671434</t>
+          <t>-76.9488912</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Avenida Los Frutales / Calle s / n</t>
+          <t>Avenida Metropolitana / Calle s / n</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11108,22 +11108,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>I-383464</t>
+          <t>I-109806</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-12.0585433</t>
+          <t>-11.9751356</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>-76.9673909</t>
+          <t>-76.7717618</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Avenida Los Frutales / Calle s / n</t>
+          <t>Avenida Malecón Manco Cápac / Calle Los Robles</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11155,27 +11155,27 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>I-383465</t>
+          <t>I-109084</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-12.0579252</t>
+          <t>-11.8573551</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>-76.967642</t>
+          <t>-77.0680587</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Avenida Los Frutales / Calle s / n</t>
+          <t>Avenida Lecaros / Calle s / n</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11202,27 +11202,27 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>I-1987</t>
+          <t>I-108893</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-12.1429363</t>
+          <t>-12.1876693</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>-77.0259837</t>
+          <t>-76.9586899</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Circuito de Playas / Quebrada de Armendariz</t>
+          <t>Avenida Miguel Iglesias / Los Nardos</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11249,27 +11249,27 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>I-5750</t>
+          <t>I-105255</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-12.0547422</t>
+          <t>-12.0240107</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>-77.0450958</t>
+          <t>-76.9774565</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Avenida República de Venezuela / Jirón Huaraz</t>
+          <t>Avenida Malecon Miguel Checa Eguiguren / Jirón Los Paujiles</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11296,27 +11296,27 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>I-254410</t>
+          <t>I-104809</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-12.0492379</t>
+          <t>-12.167074</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>-77.0537602</t>
+          <t>-76.9518449</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Avenida Tingo María / Jirón Zorritos</t>
+          <t>Avenida Pachacútec / Avenida Villa María</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11343,27 +11343,27 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>I-1367</t>
+          <t>I-102917</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-11.8669626</t>
+          <t>-12.0144721</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>-77.01148</t>
+          <t>-76.8392907</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Avenida Jaime Zubieta Calderon / Calle s / n</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11390,2330 +11390,27 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>I-16822</t>
+          <t>I-100271</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-11.9676645</t>
+          <t>-12.2201736</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>-76.7429975</t>
+          <t>-76.9304303</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Avenida Nicolás Ayllón / Calle s / n</t>
+          <t>Avenida José Carlos Mariátegui / Calle B</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>I-5821</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-12.1716522</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-77.0164978</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Avenida Prolongación Paseo de la República / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>I-1526</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>-11.9648709</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-77.0617062</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Avenida Maestro Peruano / Avenida Metropolitana</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>I-205019</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-12.0393355</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-76.9739592</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>I-3282</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-12.0708299</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-77.04071</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Avenida General Salaverry / Jirón Nazca</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>I-346213</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-12.0877731</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>-77.0610377</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Avenida Faustino Sanchez Carrión / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>I-351791</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>-12.0727128</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>-77.0468834</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Avenida General Santa Cruz / Jirón Huáscar</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>I-352859</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>-12.0799537</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>-77.0394574</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Avenida Edgardo Rebagliati / Jirón Almirante Martin Guisse</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>I-352862</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>-12.0797382</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>-77.0410486</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Avenida Edgardo Rebagliati / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>I-6373</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>-12.0661888</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>-76.9433793</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Avenida Javier Prado Este / Ricardo Palma</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>I-3638</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>-12.0766478</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-77.0287479</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Avenida México / Avenida Paseo de la República / Vía Expresa Luis Fernán Bedoya Reyes</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>I-321779</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>-12.0703745</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>-77.0300959</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Avenida Iquitos / Avenida Isabel La Católica</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>I-1412</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>-12.0045599</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>-77.0630915</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Avenida Angélica Gamarra / Avenida El Sol de Oro / Jirón Sol de Oro</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>I-124033</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>-11.9409618</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-77.0781257</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Avenida Los Próceres de Huandoy / Calle 53</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>I-124034</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>-11.9389613</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>-77.0778385</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Avenida La Cordialidad / Calle 53</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>I-5687</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>-12.3001175</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>-76.8453082</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Antigua Panamericana Sur / Avenida Industrial</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>I-2090</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>-12.0957573</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-77.0707891</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Avenida Brasil / Jirón Arica / Jirón Salaverry</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>I-301595</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>-12.0936892</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-77.0585066</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Avenida Javier Prado Oeste / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>I-305777</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-12.0923903</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>-77.0706856</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Avenida Antonio José de Sucre / Jirón Francisco Bolognesi</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>I-311878</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-12.0932685</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>-77.0745855</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Jirón Alfonso Ugarte / Jirón Mariscal Ramon Castilla</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>I-306730</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>-12.0740921</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>-77.0530194</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Avenida Afranio de Mello Franco / Avenida Brasil / Calle Coraceros</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>I-16295</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>-12.2196107</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>-76.8729937</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Calle 3 / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>I-16615</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>-11.8672848</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>-77.0778094</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Calle 9 de Julio / Calle La Victoria</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>I-574449</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-12.2984865</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-76.7807326</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Avenida Pampa Pacta / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>I-574452</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>-12.2904145</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>-76.7624038</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Avenida Pampa Pacta / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>I-1373</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>-12.038727</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>-77.032335</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Avenida Francisco Pizarro / Avenida Prolongación Tacna</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>I-316755</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>-12.0336977</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>-77.0387761</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Avenida Felipe Arancibia / Avenida Francisco Pizarro / Jirón General Vidal</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>I-6352</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>-12.0853873</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>-76.9839922</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Avenida Circunvalación / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>I-1619</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-12.029503</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>-77.0197801</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Avenida Prolongación Tacna / Túnel San Martín / Túnel Santa Rosa</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>I-6325</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-12.1655068</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>-76.97382</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Avenida Ramón Vargas Machuca / Calle J. Morales</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>I-6670</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-12.0634581</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-76.9999583</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Avenida Circunvalación / Avenida Nicolás de Ayllón</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>I-329470</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-12.0802446</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>-77.0024316</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Avenida Del Aire / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>I-329472</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>-12.0792718</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-77.0003994</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Avenida Del Aire / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>I-1354</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>-12.0383943</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-77.0435524</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Avenida Alfonso Ugarte / Avenida Caquetá</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>I-159328</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>-11.9707867</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-77.112795</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Calle s / n / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>I-14939</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-12.0574582</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-76.9716404</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Avenida Los Cipreses / Avenida Minería / Avenida Nicolás de Ayllón</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>I-4396</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-12.1288367</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-76.9999211</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Avenida Alfredo Benavides / Jirón Preciados</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>I-1626</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>-12.1070413</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-77.0267452</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Avenida Paseo de la República / Vía Expresa Luis Fernán Bedoya Reyes</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>I-16788</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>-12.2408504</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-76.9115894</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Avenida Lima / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>I-338594</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-12.1924407</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-76.9536536</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Avenida Modelo / Calle B</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>I-338602</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>-12.1933549</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-76.9552545</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Avenida Micaela Bastidas / Avenida Modelo</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>I-6270</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>-12.1905646</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-76.9504335</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Avenida Modelo / Avenida Revolución</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>I-6263</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>-12.1955387</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-76.9590457</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Avenida Mariano Pastor Sevilla / Avenida Modelo</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>I-338597</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>-12.18867</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>-76.9471582</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>Avenida Modelo / Calle E</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>I-15201</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>-12.1763323</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>-76.940786</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Avenida Nicolás de Piérola / Pasaje Peruanidad</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>I-322764</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>-12.0786609</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-77.0569041</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>Avenida Brasil / Avenida Francisco Javier Mariátegui</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>I-322991</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>-12.0711584</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-77.0505324</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Avenida Brasil / Avenida Colombia / Avenida José María Plaza</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>I-352243</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>-12.0780242</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-77.0806041</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Avenida de La Marina / Calle Ciclovía La Marina</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>I-395918</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>-12.0843183</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>-77.0647771</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Avenida de La Marina / Calle s / n</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>150101</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>I-6758</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>-12.0678335</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>-77.0605732</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Avenida Paso de los Andes / Plaza de la Bandera</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
